--- a/scenario/scenario 1.xlsx
+++ b/scenario/scenario 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c7dd620d9e945120/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sneha\OneDrive\Desktop\foodiehub pro\scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81974230-6EF6-482E-AA2F-85790527C5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B515AC-990A-4A44-BD50-28051DE33C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06AD5FD1-1349-49AE-AA6D-24E2E0AE81AE}"/>
   </bookViews>
@@ -33,6 +33,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -729,8 +751,9 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
+      <c r="A2" s="2" cm="1">
+        <f t="array" aca="1" ref="A2" ca="1">A2:D331</f>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
